--- a/public/exports-60-250/29208654.xlsx
+++ b/public/exports-60-250/29208654.xlsx
@@ -2164,7 +2164,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352260</t>
+          <t xml:space="preserve">311352257</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352251</t>
+          <t xml:space="preserve">311352250</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352309</t>
+          <t xml:space="preserve">311352303</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
